--- a/data/daily/2026-07/2026-07-29.xlsx
+++ b/data/daily/2026-07/2026-07-29.xlsx
@@ -2117,7 +2117,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2127,10 +2127,10 @@
         <v>2.5</v>
       </c>
       <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2149,10 +2149,10 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>

--- a/data/daily/2026-07/2026-07-29.xlsx
+++ b/data/daily/2026-07/2026-07-29.xlsx
@@ -774,7 +774,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -782,27 +782,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
+          <t>[카사베르디] 유기농 레드와인 비니거 스틱 3박스(총42포)+리센느포토카드&amp;포스터+추가사은품 증정</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>36,300원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/13709524</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260729090254_d7ad33c22cc94b9a9af1791f9271986d.png</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -922,34 +922,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>[그레인온] 카무트 브랜드밀 프리미엄 효소90 3개월분+10포+쇼핑백 증정</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>56,900원</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/13215071</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260714110741_0c5ee4d65772453582e5a95846726854.jpg</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -957,34 +957,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)수저세트</t>
+          <t>2입 추가 증정 "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12860133</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260728104438_e58225d6ca9544398c5df7af6381981e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260703103417_e8e422c5cf9740e3bfc2662a9aaa1eef.jpg</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -992,27 +992,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[그레인온] 카무트 브랜드밀 프리미엄 효소90 3개월분+10포+쇼핑백 증정</t>
+          <t>[한끼통살] 단백질 든든형 닭가슴살 21일 식단관리+(증정)수저세트</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>56,900원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13215071</t>
+          <t>https://gift.kakao.com/product/12860133</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260714110741_0c5ee4d65772453582e5a95846726854.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260728104438_e58225d6ca9544398c5df7af6381981e.jpg</t>
         </is>
       </c>
     </row>
@@ -1027,34 +1027,34 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월분+10포 추가+파로차진액스틱5포+쇼핑백 증정</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>45,000원</t>
+          <t>64,900원</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/13255641</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260727085300_3f36250cc75c4cdfae5ccb2a61380afa.jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1062,27 +1062,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 파로효소 캡슐레이션 3개월분+10포 추가+파로차진액스틱5포+쇼핑백 증정</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>64,900원</t>
+          <t>45,000원</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13255641</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260727085300_3f36250cc75c4cdfae5ccb2a61380afa.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1218,34 +1218,34 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953529&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/vXg1N5D0xbSNweDPvvl2994953529_00_00vXg1N5D0xbSNweDPvvl2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>자연관 이뮨 멀티비타민 미네랄 4병</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1268,19 +1268,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602124&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251216/mSQXyRQCV8ORV8edPm4n613602124_00_01mSQXyRQCV8ORV8edPm4n.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>동국제약 리포좀 비타민C 30정</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1303,19 +1303,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910679&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250829/3zNHA2Xp859SKsazXUwt610910679_00_003zNHA2Xp859SKsazXUwt.png</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>대웅제약 루테인 30정 30일분</t>
+          <t>대웅제약 철분 30정 30일분</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OgijyKEodb7qfhaHtw3p600000133_00_00OgijyKEodb7qfhaHtw3p.png</t>
         </is>
       </c>
     </row>
@@ -1358,12 +1358,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
+          <t>종근당건강 락토핏 골드</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1373,19 +1373,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627034&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580521&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251202/GgXyFjpcjCiNxq7s9y0h032627034_00_00GgXyFjpcjCiNxq7s9y0h.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260522/0jgRGoNZEcwwrbTgrqVw591580521_00_000jgRGoNZEcwwrbTgrqVw.jpg</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1393,34 +1393,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>종근당건강 락토핏 골드</t>
+          <t>대웅제약 바나바잎 추출물 30정 (30일분)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591580521&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260522/0jgRGoNZEcwwrbTgrqVw591580521_00_000jgRGoNZEcwwrbTgrqVw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1428,34 +1428,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>안국약품 브이팩 다이어트 유산균 올인원 멀티 비타민 7포</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=968235549&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/kQh0cYBVEEUhZLYsuKrQ968235549_00_00kQh0cYBVEEUhZLYsuKrQ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>대웅제약 녹차카테킨 30정 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1478,19 +1478,19 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000136&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/5KgtE2Z5pfS6P1gIBIIh600000136_00_005KgtE2Z5pfS6P1gIBIIh.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>대웅제약 프로폴리스 츄어블 30정 30일분</t>
+          <t>오브맘 다이어트 홀릭 15일분</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000150&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624075&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250409/Kpov6WvmW02F4pW9qB4z600000150_00_00Kpov6WvmW02F4pW9qB4z.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250519/2rLyPRrrXXN6XdvBMjj5913624075_00_002rLyPRrrXXN6XdvBMjj5.jpg</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1533,12 +1533,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>락피도 티니핑 철분스틱 12포 12일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>락피도</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1548,12 +1548,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=951817120&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260226/Lb8S1LqMvpkz0uUPx4SJ951817120_00_01Lb8S1LqMvpkz0uUPx4SJ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1654,34 +1654,34 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[급찐급빠] 칼로 스탑/컨트롤 PLUS 15포+15포 더블기획 3종 (1개월분) (OY단독)</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>칼로(Kalo)</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000243670&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024367007ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1689,34 +1689,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CJ 바이오코어 비피더스 다이어트 유산균 14캡슐 (2주분)</t>
+          <t>[급찐급빠] 칼로 스탑/컨트롤 PLUS 15포+15포 더블기획 3종 (1개월분) (OY단독)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000259858&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000243670&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025985804ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024367007ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1724,34 +1724,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>35,800원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492937ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1759,34 +1759,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>35,800원</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492937ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1794,34 +1794,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
+          <t>CJ 바이오코어 비피더스 다이어트 유산균 14캡슐 (2주분)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59,000원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249509&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000259858&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024950901ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025985804ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1829,27 +1829,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[7월 올영픽/파격특가] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13,000원</t>
+          <t>59,000원</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249509&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355459ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024950901ko.png?l=ko</t>
         </is>
       </c>
     </row>
@@ -1864,34 +1864,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[7월 올영픽] 콜레올로지 컷팅 젤리 레몬/키위/석류 10+2+2포 기획</t>
+          <t>칼로 나이트 Relax 15포 (15일분)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>18,800원</t>
+          <t>14,700원</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000183645&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000222551&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018364582ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022255103ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1899,27 +1899,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[7월 올영픽/1일 1정] 바이탈뷰티 메타그린 슬림업 30일 (+15일)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>바이탈뷰티</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29,300원</t>
+          <t>55,900원</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248462&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024846223ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308648ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -1934,27 +1934,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 10종 택 1</t>
+          <t>[올영단독] 칼로 스탑/컨트롤 PLUS 15포 2종</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>씨제이웰케어</t>
+          <t>칼로(Kalo)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5,900원</t>
+          <t>10,900원</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000186228&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786103ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018622875ko.jpg?l=ko</t>
         </is>
       </c>
     </row>
@@ -1969,7 +1969,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2011,47 +2011,47 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>27.5</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -2061,26 +2061,26 @@
         <v>17.5</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2117,7 +2117,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -2139,7 +2139,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2161,7 +2161,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -2171,12 +2171,56 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
